--- a/binomial_model/files/binomial_sensitivity_analysis.xlsx
+++ b/binomial_model/files/binomial_sensitivity_analysis.xlsx
@@ -445,16 +445,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.6012146707558496</v>
+        <v>0.4848338253184952</v>
       </c>
       <c r="C2">
-        <v>0.06750964172823673</v>
+        <v>0.1531052137300659</v>
       </c>
       <c r="D2">
-        <v>0.6574069446339277</v>
+        <v>0.5171798720861041</v>
       </c>
       <c r="E2">
-        <v>0.0596162990520057</v>
+        <v>0.1507423897472487</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -462,16 +462,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.01112532050175621</v>
+        <v>0.005618446599194071</v>
       </c>
       <c r="C3">
-        <v>0.01051459074654799</v>
+        <v>0.04428302899706402</v>
       </c>
       <c r="D3">
-        <v>0.01255401901110662</v>
+        <v>0.02221348144117663</v>
       </c>
       <c r="E3">
-        <v>0.0021331950799535</v>
+        <v>0.00924934627858187</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -479,16 +479,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.006768384797032791</v>
+        <v>0.03087889107804935</v>
       </c>
       <c r="C4">
-        <v>0.006567285610270984</v>
+        <v>0.02548464669524808</v>
       </c>
       <c r="D4">
-        <v>0.007986040396636081</v>
+        <v>0.01272633892149753</v>
       </c>
       <c r="E4">
-        <v>0.001150777867933456</v>
+        <v>0.00972865449878246</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -496,16 +496,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.0025345875871529</v>
+        <v>0.01782810631746606</v>
       </c>
       <c r="C5">
-        <v>0.005674450952871809</v>
+        <v>0.01965734774264354</v>
       </c>
       <c r="D5">
-        <v>0.003929044336558327</v>
+        <v>0.005992345203383379</v>
       </c>
       <c r="E5">
-        <v>0.0007258512663164875</v>
+        <v>0.003030552658759401</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -513,16 +513,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.004006901942719179</v>
+        <v>-0.007641808472762962</v>
       </c>
       <c r="C6">
-        <v>0.01354013374355707</v>
+        <v>0.03116869949857479</v>
       </c>
       <c r="D6">
-        <v>0.02022407567381494</v>
+        <v>0.01031830074130538</v>
       </c>
       <c r="E6">
-        <v>0.004427672676600248</v>
+        <v>0.006517581771309405</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -530,16 +530,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>0.2461867927323429</v>
+        <v>0.4345515376864588</v>
       </c>
       <c r="C7">
-        <v>0.04699437822680519</v>
+        <v>0.1873339140682213</v>
       </c>
       <c r="D7">
-        <v>0.2892858971048997</v>
+        <v>0.4948859021356314</v>
       </c>
       <c r="E7">
-        <v>0.03228698066608706</v>
+        <v>0.134328419975726</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -547,16 +547,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.04274757573567647</v>
+        <v>0.007586944695261425</v>
       </c>
       <c r="C8">
-        <v>0.02264817771483357</v>
+        <v>0.0358436701110687</v>
       </c>
       <c r="D8">
-        <v>0.06788184809555442</v>
+        <v>0.03115453966291856</v>
       </c>
       <c r="E8">
-        <v>0.01248727096694644</v>
+        <v>0.01748395076945533</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -564,16 +564,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.000106785915390182</v>
+        <v>-0.0003059273341327757</v>
       </c>
       <c r="C9">
-        <v>0.0006569129181377971</v>
+        <v>0.001728616788714088</v>
       </c>
       <c r="D9">
-        <v>5.328588274564632E-05</v>
+        <v>3.291626487240874E-05</v>
       </c>
       <c r="E9">
-        <v>7.430566138594259E-06</v>
+        <v>1.850366969200299E-05</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -581,16 +581,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0.01412378940905921</v>
+        <v>-0.0001025124884972497</v>
       </c>
       <c r="C10">
-        <v>0.01094038466804241</v>
+        <v>0.0404013933116254</v>
       </c>
       <c r="D10">
-        <v>0.01578537039787409</v>
+        <v>0.02332461569539771</v>
       </c>
       <c r="E10">
-        <v>0.001785987882973863</v>
+        <v>0.009504383815353368</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -598,16 +598,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>0.0006813343752001337</v>
+        <v>-0.001228486632364326</v>
       </c>
       <c r="C11">
-        <v>0.001636297753573987</v>
+        <v>0.006568739853040299</v>
       </c>
       <c r="D11">
-        <v>0.0003432477910645831</v>
+        <v>0.0003269301155483321</v>
       </c>
       <c r="E11">
-        <v>6.521024654375897E-05</v>
+        <v>0.0001318826180459853</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -615,16 +615,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>-0.0004502337416300917</v>
+        <v>0.0006775930811928798</v>
       </c>
       <c r="C12">
-        <v>0.0017273048668306</v>
+        <v>0.003885650755969588</v>
       </c>
       <c r="D12">
-        <v>0.0004378271837445342</v>
+        <v>0.0001740995713850244</v>
       </c>
       <c r="E12">
-        <v>7.169474008239487E-05</v>
+        <v>6.099209222069497E-05</v>
       </c>
     </row>
   </sheetData>
@@ -659,16 +659,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.4522016985115181</v>
+        <v>0.2263246218766954</v>
       </c>
       <c r="C2">
-        <v>0.06426171731443386</v>
+        <v>0.1387290426268852</v>
       </c>
       <c r="D2">
-        <v>0.4896771323667794</v>
+        <v>0.2722177268416562</v>
       </c>
       <c r="E2">
-        <v>0.05024938340349491</v>
+        <v>0.0843115022958041</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -676,16 +676,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>-0.001275105978108423</v>
+        <v>0.007955751006047337</v>
       </c>
       <c r="C3">
-        <v>0.007389795236681082</v>
+        <v>0.02425120592082214</v>
       </c>
       <c r="D3">
-        <v>0.006659088228310458</v>
+        <v>0.009117178882287684</v>
       </c>
       <c r="E3">
-        <v>0.001131625663032665</v>
+        <v>0.00413375303328929</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -693,16 +693,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.002393646270773146</v>
+        <v>0.003043764799265684</v>
       </c>
       <c r="C4">
-        <v>0.006133296805780855</v>
+        <v>0.01933732361995401</v>
       </c>
       <c r="D4">
-        <v>0.004196395718311896</v>
+        <v>0.005841780567944182</v>
       </c>
       <c r="E4">
-        <v>0.0006922696936014159</v>
+        <v>0.004723629125233559</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -710,16 +710,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>-0.001200545020480247</v>
+        <v>0.002293938954758625</v>
       </c>
       <c r="C5">
-        <v>0.004508822286971097</v>
+        <v>0.01767530241829323</v>
       </c>
       <c r="D5">
-        <v>0.00219543858975412</v>
+        <v>0.00277285902463311</v>
       </c>
       <c r="E5">
-        <v>0.0004569981686258385</v>
+        <v>0.001649806560858226</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -727,16 +727,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.001483466364492447</v>
+        <v>0.009101379381647668</v>
       </c>
       <c r="C6">
-        <v>0.01028052370568523</v>
+        <v>0.02125079867941526</v>
       </c>
       <c r="D6">
-        <v>0.01513500782082239</v>
+        <v>0.005108421404122282</v>
       </c>
       <c r="E6">
-        <v>0.003462067817941006</v>
+        <v>0.004240359063694178</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -744,16 +744,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>0.4118634086766541</v>
+        <v>0.6917313912909991</v>
       </c>
       <c r="C7">
-        <v>0.05239130335606948</v>
+        <v>0.1728133945233105</v>
       </c>
       <c r="D7">
-        <v>0.4292728990355037</v>
+        <v>0.7411786946999666</v>
       </c>
       <c r="E7">
-        <v>0.03866990266418503</v>
+        <v>0.1706914634347899</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -761,16 +761,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.02667016962549004</v>
+        <v>0.01727277757347368</v>
       </c>
       <c r="C8">
-        <v>0.02208907768100464</v>
+        <v>0.03590822715466028</v>
       </c>
       <c r="D8">
-        <v>0.05013529378886356</v>
+        <v>0.01717475082608099</v>
       </c>
       <c r="E8">
-        <v>0.009829117055397645</v>
+        <v>0.007880275384619922</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -778,16 +778,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>3.353386863985535E-06</v>
+        <v>-8.56444847269786E-05</v>
       </c>
       <c r="C9">
-        <v>0.001175471111512694</v>
+        <v>0.003120516175698942</v>
       </c>
       <c r="D9">
-        <v>0.0001781919038569871</v>
+        <v>7.72477173529509E-05</v>
       </c>
       <c r="E9">
-        <v>2.32031361434416E-05</v>
+        <v>3.893365265930005E-05</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -795,16 +795,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0.006168138994991206</v>
+        <v>0.006084388862533573</v>
       </c>
       <c r="C10">
-        <v>0.008436309350809718</v>
+        <v>0.02209222695465739</v>
       </c>
       <c r="D10">
-        <v>0.008412055629060573</v>
+        <v>0.006657697411868759</v>
       </c>
       <c r="E10">
-        <v>0.001034250239091239</v>
+        <v>0.003080148649862244</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -812,16 +812,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>0.003669843291657434</v>
+        <v>0.002892869813708931</v>
       </c>
       <c r="C11">
-        <v>0.005954134444270239</v>
+        <v>0.01639875307321705</v>
       </c>
       <c r="D11">
-        <v>0.00468957473007544</v>
+        <v>0.003978236323392536</v>
       </c>
       <c r="E11">
-        <v>0.0007057623186616712</v>
+        <v>0.001314249338098966</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -829,16 +829,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.02265005578165565</v>
+        <v>-0.004771530560673976</v>
       </c>
       <c r="C12">
-        <v>0.01392753652717375</v>
+        <v>0.03860708967117529</v>
       </c>
       <c r="D12">
-        <v>0.02996710198459045</v>
+        <v>0.01832218638756098</v>
       </c>
       <c r="E12">
-        <v>0.002963632994827064</v>
+        <v>0.004156558389807039</v>
       </c>
     </row>
   </sheetData>
